--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488070_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488070_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0705</v>
+        <v>4.6008</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6488</v>
+        <v>5.9544</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5783</v>
+        <v>-1.3536</v>
       </c>
       <c r="G2" t="n">
         <v>3.8041</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.3332</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5505</v>
+        <v>-0.2449</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3129</v>
+        <v>-0.0883</v>
       </c>
       <c r="V2" t="n">
         <v>0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1265</v>
+        <v>2.4165</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7101</v>
+        <v>6.1405</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5836</v>
+        <v>-3.724</v>
       </c>
       <c r="G3" t="n">
         <v>1.288</v>
@@ -688,13 +688,13 @@
         <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8682</v>
+        <v>-0.5782</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1745</v>
+        <v>-0.7441</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3063</v>
+        <v>0.1659</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0545</v>
+        <v>0.1334</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0836</v>
+        <v>2.3311</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0292</v>
+        <v>-2.1976</v>
       </c>
       <c r="G4" t="n">
         <v>-1.5505</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7943</v>
+        <v>-0.1267</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8811</v>
+        <v>0.1286</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0868</v>
+        <v>-0.2553</v>
       </c>
       <c r="V4" t="n">
         <v>1.8107</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4145</v>
+        <v>-0.6434</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4077</v>
+        <v>0.572</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8223</v>
+        <v>-1.2154</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9593</v>
@@ -844,13 +844,13 @@
         <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.2965</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2386</v>
+        <v>-0.0743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1709</v>
+        <v>-0.2222</v>
       </c>
       <c r="V5" t="n">
         <v>1.2071</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>M. BAMADU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2731</v>
+        <v>-2.385</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.17</v>
+        <v>1.1907</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1031</v>
+        <v>-3.5757</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2569</v>
+        <v>-0.6684</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2569</v>
+        <v>2.6472</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-3.3156</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9282</v>
+        <v>1.8567</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9282</v>
+        <v>3.1748</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.3181</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6713</v>
+        <v>-2.5251</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6713</v>
+        <v>-0.5276</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.9975</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7751</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9733</v>
+        <v>-1.1893</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1747</v>
+        <v>-0.569</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1248</v>
+        <v>-0.3468</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2995</v>
+        <v>-0.2222</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0704</v>
+        <v>-1.5441</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0704</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BAMADU</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8196</v>
+        <v>-2.3854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9246</v>
+        <v>-2.17</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7442</v>
+        <v>-0.2155</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6684</v>
+        <v>0.2569</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6472</v>
+        <v>0.2569</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.3156</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8567</v>
+        <v>0.9282</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1748</v>
+        <v>0.9282</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3181</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5251</v>
+        <v>-0.6713</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5276</v>
+        <v>-0.6713</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9975</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1893</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0036</v>
+        <v>0.0624</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6129</v>
+        <v>-0.1248</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3907</v>
+        <v>0.1872</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5441</v>
+        <v>0.0704</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4142</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2052</v>
+        <v>-2.9478</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3215</v>
+        <v>-2.0262</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8837</v>
+        <v>-0.9215</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0771</v>
+        <v>-4.8302</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7302999999999999</v>
+        <v>-1.5567</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8074</v>
+        <v>-3.2736</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3873</v>
+        <v>-0.8478</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2668</v>
+        <v>0.3096</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1205</v>
+        <v>-1.1574</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4645</v>
+        <v>-3.9824</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5365</v>
+        <v>-1.8662</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.928</v>
+        <v>-2.1162</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-3.1716</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2705</v>
+        <v>-0.5516</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6719000000000001</v>
+        <v>-0.4211</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5986</v>
+        <v>-0.1305</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.218</v>
+        <v>3.4252</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4074</v>
+        <v>2.4142</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8107</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3602</v>
+        <v>-3.1179</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3627</v>
+        <v>-1.2608</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9975</v>
+        <v>-1.8571</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3854</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8975</v>
+        <v>-0.6553</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5231</v>
+        <v>-0.3827</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8701</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.659</v>
+        <v>-4.2104</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4567</v>
+        <v>-1.0741</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2023</v>
+        <v>-3.1364</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8302</v>
+        <v>-0.0771</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5567</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2736</v>
+        <v>-0.8074</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8478</v>
+        <v>2.3873</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3096</v>
+        <v>2.2668</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1574</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9824</v>
+        <v>-2.4645</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8662</v>
+        <v>-1.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1162</v>
+        <v>-0.928</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1716</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2628</v>
+        <v>0.2652</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8515</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4113</v>
+        <v>0.3459</v>
       </c>
       <c r="V10" t="n">
-        <v>3.4252</v>
+        <v>-2.218</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4142</v>
+        <v>-0.4074</v>
       </c>
       <c r="X10" t="n">
-        <v>1.0109</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0139</v>
+        <v>-7.3308</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.889</v>
+        <v>-2.4586</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.125</v>
+        <v>-4.8722</v>
       </c>
       <c r="G11" t="n">
         <v>-5.204</v>
@@ -1312,13 +1312,13 @@
         <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0854</v>
+        <v>-1.4023</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0387</v>
+        <v>-0.6083</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0467</v>
+        <v>-0.794</v>
       </c>
       <c r="V11" t="n">
         <v>0.2666</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.494</v>
+        <v>-15.87</v>
       </c>
       <c r="E12" t="n">
-        <v>6.5749</v>
+        <v>7.199</v>
       </c>
       <c r="F12" t="n">
-        <v>-23.0692</v>
+        <v>-23.069</v>
       </c>
       <c r="G12" t="n">
         <v>-10.3259</v>
       </c>
       <c r="H12" t="n">
-        <v>3.085499999999999</v>
+        <v>3.0855</v>
       </c>
       <c r="I12" t="n">
         <v>-13.4116</v>
@@ -1369,7 +1369,7 @@
         <v>15.3846</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1871</v>
+        <v>1.187099999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-26.8978</v>
@@ -1390,10 +1390,10 @@
         <v>14.8668</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.808999999999999</v>
+        <v>-4.1852</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4129</v>
+        <v>-2.7889</v>
       </c>
       <c r="U12" t="n">
         <v>-1.3962</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0937</v>
+        <v>6.2779</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9413</v>
+        <v>6.2469</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1524</v>
+        <v>0.031</v>
       </c>
       <c r="G13" t="n">
         <v>4.4601</v>
@@ -1468,13 +1468,13 @@
         <v>2.9733</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4264</v>
+        <v>1.6106</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0589</v>
+        <v>0.3646</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3675</v>
+        <v>1.246</v>
       </c>
       <c r="V13" t="n">
         <v>0.6036</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6228</v>
+        <v>5.6518</v>
       </c>
       <c r="E14" t="n">
-        <v>4.894</v>
+        <v>4.1888</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2712</v>
+        <v>1.463</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0806</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5832</v>
+        <v>-2.9646</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4974</v>
+        <v>3.7464</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7344</v>
+        <v>3.0968</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6502</v>
+        <v>-1.0285</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0842</v>
+        <v>4.1254</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6538</v>
+        <v>-2.3151</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.067</v>
+        <v>-1.9361</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4132</v>
+        <v>-0.379</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8354</v>
+        <v>0.6718</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5471</v>
+        <v>-0.1329</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2883</v>
+        <v>0.8047</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8107</v>
+        <v>2.4142</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2668</v>
+        <v>3.5858</v>
       </c>
       <c r="E15" t="n">
-        <v>3.272</v>
+        <v>4.2827</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9948</v>
+        <v>-0.6969</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7818000000000001</v>
+        <v>2.0806</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.9646</v>
+        <v>1.5832</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7464</v>
+        <v>0.4974</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0968</v>
+        <v>2.7344</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0285</v>
+        <v>2.6502</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1254</v>
+        <v>0.0842</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3151</v>
+        <v>-0.6538</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9361</v>
+        <v>-1.067</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.379</v>
+        <v>0.4132</v>
       </c>
       <c r="P15" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7131999999999999</v>
+        <v>0.7984</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0497</v>
+        <v>-0.0641</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3365</v>
+        <v>0.8625</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4142</v>
+        <v>-1.4737</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4142</v>
+        <v>1.8107</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.2843</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7158</v>
+        <v>2.8714</v>
       </c>
       <c r="E16" t="n">
-        <v>3.47</v>
+        <v>2.3495</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2457</v>
+        <v>0.522</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0927</v>
@@ -1702,13 +1702,13 @@
         <v>2.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1017</v>
+        <v>1.2573</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1036</v>
+        <v>0.983</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0019</v>
+        <v>0.2743</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8701</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6301</v>
+        <v>0.9301</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9137</v>
+        <v>0.721</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2836</v>
+        <v>0.2091</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5303</v>
+        <v>-1.0165</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4883</v>
+        <v>0.1181</v>
       </c>
       <c r="I18" t="n">
-        <v>0.042</v>
+        <v>-1.1346</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8518</v>
+        <v>0.7728</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6911</v>
+        <v>1.251</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1607</v>
+        <v>-0.4782</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3215</v>
+        <v>-1.7893</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2028</v>
+        <v>-1.1329</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1187</v>
+        <v>-0.6563</v>
       </c>
       <c r="P18" t="n">
+        <v>2.3787</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.1982</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.1893</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0984</v>
+        <v>-0.0247</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7488</v>
+        <v>-0.6533</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6504</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6036</v>
+        <v>-0.4074</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3522</v>
+        <v>0.89</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0252</v>
+        <v>1.1174</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6731</v>
+        <v>-0.2274</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6862</v>
+        <v>1.5303</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4291</v>
+        <v>1.4883</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1154</v>
+        <v>0.042</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2859</v>
+        <v>2.8518</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0404</v>
+        <v>2.6911</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2455</v>
+        <v>0.1607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5996</v>
+        <v>-1.3215</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4695</v>
+        <v>-1.2028</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1301</v>
+        <v>-0.1187</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.334</v>
+        <v>0.1615</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0624</v>
+        <v>-0.545</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2717</v>
+        <v>0.7065</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1902</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3135</v>
+        <v>1.3309</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1233</v>
+        <v>-0.6731</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0165</v>
+        <v>0.6862</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1181</v>
+        <v>-0.4291</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1346</v>
+        <v>1.1154</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7728</v>
+        <v>1.2859</v>
       </c>
       <c r="K20" t="n">
-        <v>1.251</v>
+        <v>0.0404</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4782</v>
+        <v>1.2455</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7893</v>
+        <v>-0.5996</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1329</v>
+        <v>-0.4695</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6563</v>
+        <v>-0.1301</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.0284</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0608</v>
+        <v>0.2432</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2962</v>
+        <v>-0.2717</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4168</v>
+        <v>-0.9735</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8925</v>
+        <v>2.2914</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3093</v>
+        <v>-3.2649</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8397</v>
+        <v>1.1311</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3524</v>
+        <v>0.2358</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5127</v>
+        <v>0.8953</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6347</v>
+        <v>3.5161</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2775</v>
+        <v>2.1059</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6428</v>
+        <v>1.4101</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.205</v>
+        <v>-2.385</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0748</v>
+        <v>-1.8702</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1301</v>
+        <v>-0.5148</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1982</v>
+        <v>-3.1716</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4912</v>
+        <v>0.6884</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7254</v>
+        <v>0.2067</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2342</v>
+        <v>0.4817</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4521</v>
+        <v>-1.5831</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3933</v>
+        <v>-0.33</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8454</v>
+        <v>-1.2531</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1311</v>
+        <v>-1.8397</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2358</v>
+        <v>-2.3524</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8953</v>
+        <v>0.5127</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5161</v>
+        <v>-0.6347</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1059</v>
+        <v>-1.2775</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4101</v>
+        <v>0.6428</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.385</v>
+        <v>-1.205</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8702</v>
+        <v>-1.0748</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5148</v>
+        <v>-0.1301</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2097</v>
+        <v>0.3249</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3085</v>
+        <v>0.503</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0988</v>
+        <v>-0.1781</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.9474</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7166</v>
+        <v>-1.664</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2544</v>
+        <v>-0.3376</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4622</v>
+        <v>-1.3264</v>
       </c>
       <c r="G23" t="n">
         <v>1.3968</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3451</v>
+        <v>0.7076</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4257</v>
+        <v>0.4911</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.2165</v>
       </c>
       <c r="V23" t="n">
         <v>0.1962</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.4941</v>
+        <v>17.8522</v>
       </c>
       <c r="E24" t="n">
-        <v>23.0691</v>
+        <v>23.069</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.575200000000001</v>
+        <v>-5.216699999999999</v>
       </c>
       <c r="G24" t="n">
         <v>10.326</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.085399999999999</v>
+        <v>-3.0854</v>
       </c>
       <c r="I24" t="n">
         <v>13.4116</v>
@@ -2326,13 +2326,13 @@
         <v>17.8399</v>
       </c>
       <c r="S24" t="n">
-        <v>4.809099999999999</v>
+        <v>6.1674</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3961</v>
+        <v>1.3963</v>
       </c>
       <c r="U24" t="n">
-        <v>3.413</v>
+        <v>4.7709</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6145</v>
